--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360884</v>
+        <v>122360869</v>
       </c>
       <c r="B2" t="n">
-        <v>97129</v>
+        <v>57390</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,35 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -773,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 bestånd</t>
+          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +778,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360869</v>
+        <v>122360884</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>97129</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,31 +932,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1019,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spår av födosökande och uthackat gammalt bohål</t>
+          <t>2 bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,6 +1027,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360869</v>
+        <v>122360884</v>
       </c>
       <c r="B2" t="n">
-        <v>57390</v>
+        <v>97139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -769,7 +773,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spår av födosökande och uthackat gammalt bohål</t>
+          <t>2 bestånd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,6 +782,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -920,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360884</v>
+        <v>122360869</v>
       </c>
       <c r="B4" t="n">
-        <v>97129</v>
+        <v>57390</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,35 +937,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1018,7 +1019,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>2 bestånd</t>
+          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1027,7 +1028,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122360884</v>
       </c>
       <c r="B2" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>122360856</v>
       </c>
       <c r="B3" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -928,7 +928,7 @@
         <v>122360869</v>
       </c>
       <c r="B4" t="n">
-        <v>57390</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122360884</v>
       </c>
       <c r="B2" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360856</v>
+        <v>122360869</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,35 +817,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -899,6 +891,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360869</v>
+        <v>122360856</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,27 +938,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1015,11 +1020,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122360884</v>
       </c>
       <c r="B2" t="n">
-        <v>97156</v>
+        <v>97165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,11 +692,6 @@
       </c>
       <c r="E2" t="n">
         <v>221945</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -801,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360869</v>
+        <v>122360856</v>
       </c>
       <c r="B3" t="n">
-        <v>57395</v>
+        <v>57532</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,27 +812,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>103021</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -891,11 +889,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +915,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360856</v>
+        <v>122360869</v>
       </c>
       <c r="B4" t="n">
-        <v>57532</v>
+        <v>57395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,35 +931,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1020,6 +1000,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360884</v>
+        <v>122360869</v>
       </c>
       <c r="B2" t="n">
-        <v>97165</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100049</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -768,7 +769,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>2 bestånd</t>
+          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +778,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -799,7 +799,7 @@
         <v>122360856</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,6 +813,11 @@
       </c>
       <c r="E3" t="n">
         <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -915,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360869</v>
+        <v>122360884</v>
       </c>
       <c r="B4" t="n">
-        <v>57395</v>
+        <v>97178</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,26 +932,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1004,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spår av födosökande och uthackat gammalt bohål</t>
+          <t>2 bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,6 +1027,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360856</v>
+        <v>122360884</v>
       </c>
       <c r="B3" t="n">
-        <v>57536</v>
+        <v>97191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -834,13 +834,9 @@
           <t>2</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -896,12 +892,18 @@
           <t>14:30</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2 bestånd</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -920,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360884</v>
+        <v>122360856</v>
       </c>
       <c r="B4" t="n">
-        <v>97178</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,25 +934,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -958,9 +960,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1016,18 +1022,12 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2 bestånd</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360869</v>
+        <v>122360856</v>
       </c>
       <c r="B2" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,27 +691,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -765,11 +773,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -922,10 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360856</v>
+        <v>122360869</v>
       </c>
       <c r="B4" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -938,35 +941,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1020,6 +1015,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360856</v>
+        <v>122360869</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57399</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -773,6 +765,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,7 +799,7 @@
         <v>122360884</v>
       </c>
       <c r="B3" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -925,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360869</v>
+        <v>122360856</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>57536</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -941,27 +938,35 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1015,11 +1020,6 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>14:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122360856</v>
+        <v>122360869</v>
       </c>
       <c r="B2" t="n">
-        <v>57536</v>
+        <v>57400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,35 +691,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -773,6 +765,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>14:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosökande och uthackat gammalt bohål</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122360884</v>
+        <v>122360856</v>
       </c>
       <c r="B3" t="n">
-        <v>97194</v>
+        <v>57537</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +808,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -837,9 +834,13 @@
           <t>2</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -895,18 +896,12 @@
           <t>14:30</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2 bestånd</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -925,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122360869</v>
+        <v>122360884</v>
       </c>
       <c r="B4" t="n">
-        <v>57399</v>
+        <v>97195</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -937,31 +932,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1019,7 +1018,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Spår av födosökande och uthackat gammalt bohål</t>
+          <t>2 bestånd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,6 +1027,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 513-2025 artfynd.xlsx
+++ b/artfynd/A 513-2025 artfynd.xlsx
@@ -923,7 +923,7 @@
         <v>122360884</v>
       </c>
       <c r="B4" t="n">
-        <v>97195</v>
+        <v>97198</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
